--- a/aicte_teams.xlsx
+++ b/aicte_teams.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="160">
   <si>
     <t>SIH 2026 — Final Teams (AICTE — Open Innovation)</t>
   </si>
@@ -313,6 +313,71 @@
   </si>
   <si>
     <t>8667274281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MECHFINAL#01
+[Ministry: AICTE]
+[PS: AICTE Open Innovation]</t>
+  </si>
+  <si>
+    <t>SANJAY KRISHNAN S</t>
+  </si>
+  <si>
+    <t>25UME081</t>
+  </si>
+  <si>
+    <t>7397098550</t>
+  </si>
+  <si>
+    <t>Mechanical Engineering · Year II · Sec A</t>
+  </si>
+  <si>
+    <t>RAJESH S</t>
+  </si>
+  <si>
+    <t>2510057</t>
+  </si>
+  <si>
+    <t>7639769676</t>
+  </si>
+  <si>
+    <t>SAIPRASATH.G</t>
+  </si>
+  <si>
+    <t>25UME080</t>
+  </si>
+  <si>
+    <t>9514190537</t>
+  </si>
+  <si>
+    <t>ABINAYA PRAKASH</t>
+  </si>
+  <si>
+    <t>25UIT004</t>
+  </si>
+  <si>
+    <t>8778478627</t>
+  </si>
+  <si>
+    <t>Information Technology · Year II · Sec B</t>
+  </si>
+  <si>
+    <t>GRACE EVANGELIN K</t>
+  </si>
+  <si>
+    <t>25UIT054</t>
+  </si>
+  <si>
+    <t>7397633107</t>
+  </si>
+  <si>
+    <t>JANANI JIGISHA T</t>
+  </si>
+  <si>
+    <t>25UIT069</t>
+  </si>
+  <si>
+    <t>9443056460</t>
   </si>
   <si>
     <t xml:space="preserve">SIH#IT012
@@ -897,7 +962,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1533,7 +1598,7 @@
         <v>102</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
@@ -1554,7 +1619,7 @@
         <v>102</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
@@ -1572,7 +1637,7 @@
         <v>111</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>23</v>
@@ -1584,19 +1649,19 @@
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="G31" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
@@ -1614,10 +1679,10 @@
         <v>118</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
@@ -1709,7 +1774,7 @@
         <v>123</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
@@ -1727,10 +1792,10 @@
         <v>135</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
@@ -1739,16 +1804,16 @@
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="F38" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>94</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>15</v>
@@ -1756,8 +1821,142 @@
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
     </row>
+    <row r="39" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>7</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+    </row>
+    <row r="41" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+    </row>
+    <row r="42" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+    </row>
+    <row r="43" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+    </row>
+    <row r="44" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="29">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A3:A8"/>
     <mergeCell ref="B3:B8"/>
@@ -1783,6 +1982,10 @@
     <mergeCell ref="B33:B38"/>
     <mergeCell ref="H33:H38"/>
     <mergeCell ref="I33:I38"/>
+    <mergeCell ref="A39:A44"/>
+    <mergeCell ref="B39:B44"/>
+    <mergeCell ref="H39:H44"/>
+    <mergeCell ref="I39:I44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
